--- a/numerical-workflows/v2/framework/经济/模块产销表/15_养成_角色.xlsx
+++ b/numerical-workflows/v2/framework/经济/模块产销表/15_养成_角色.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="升级" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="升阶" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="升星" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="星盘能效" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="资源汇总" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="机器明细" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升级" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升阶" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升星" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="星盘能效" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源汇总" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机器明细" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'产销阅读'!$A$1:$J$85</definedName>
